--- a/experiment/HAT+CNN_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/HAT+CNN_bestx4/Test/results-Set5/Set5.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.88</v>
+        <v>34.89</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9413</v>
+        <v>0.9414</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.71</v>
+        <v>28.69</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9201</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>32.99</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7986</v>
+        <v>0.7984</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.7</v>
+        <v>30.73</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9143</v>
+        <v>0.9146</v>
       </c>
     </row>
     <row r="7">
